--- a/Money Heist/La_Casa_de_Papel_S3E01_台词 - 副本.xlsx
+++ b/Money Heist/La_Casa_de_Papel_S3E01_台词 - 副本.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\05_达途\包浆英语\Money Heist\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\05_达途\包浆英语\Money Heist\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="22305" windowHeight="12360"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="纸钞屋 S3E01 台词" sheetId="1" r:id="rId1"/>
